--- a/courses_data/mba/MBA_Result_final.xlsx
+++ b/courses_data/mba/MBA_Result_final.xlsx
@@ -9,8 +9,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Sheet1!$1:$1048576</definedName>
@@ -163,7 +161,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -215,12 +213,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="16"/>
       <color rgb="FF000000"/>
@@ -255,22 +247,6 @@
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
@@ -338,7 +314,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -347,6 +323,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -371,16 +351,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -391,22 +371,18 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -415,35 +391,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -470,9 +438,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>54360</xdr:colOff>
+      <xdr:colOff>54000</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>1110960</xdr:rowOff>
+      <xdr:rowOff>1110600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -486,7 +454,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9562680" y="148320"/>
-          <a:ext cx="958320" cy="962640"/>
+          <a:ext cx="957960" cy="962280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -545,236 +513,237 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="51" style="1" width="3.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="1" width="4.57"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1006" min="55" style="1" width="9.13"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="1007" style="2" width="9.13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="143.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="3"/>
-      <c r="AD1" s="2"/>
-      <c r="AE1" s="4"/>
-      <c r="AF1" s="3"/>
-      <c r="AG1" s="3"/>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2"/>
-      <c r="AK1" s="2"/>
-      <c r="AL1" s="2"/>
-      <c r="AM1" s="2"/>
-      <c r="AN1" s="2"/>
-      <c r="AO1" s="2"/>
-      <c r="AP1" s="2"/>
-      <c r="AQ1" s="2"/>
-      <c r="AR1" s="2"/>
-      <c r="AS1" s="2"/>
-      <c r="AT1" s="2"/>
-      <c r="AU1" s="2"/>
-      <c r="AV1" s="2"/>
-      <c r="AW1" s="2"/>
-      <c r="AX1" s="2"/>
-      <c r="AY1" s="2"/>
-      <c r="AZ1" s="2"/>
-      <c r="BA1" s="2"/>
-      <c r="BB1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="3"/>
+      <c r="AE1" s="5"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="3"/>
+      <c r="AI1" s="3"/>
+      <c r="AJ1" s="3"/>
+      <c r="AK1" s="3"/>
+      <c r="AL1" s="3"/>
+      <c r="AM1" s="3"/>
+      <c r="AN1" s="3"/>
+      <c r="AO1" s="3"/>
+      <c r="AP1" s="3"/>
+      <c r="AQ1" s="3"/>
+      <c r="AR1" s="3"/>
+      <c r="AS1" s="3"/>
+      <c r="AT1" s="3"/>
+      <c r="AU1" s="3"/>
+      <c r="AV1" s="3"/>
+      <c r="AW1" s="3"/>
+      <c r="AX1" s="3"/>
+      <c r="AY1" s="3"/>
+      <c r="AZ1" s="3"/>
+      <c r="BA1" s="3"/>
+      <c r="BB1" s="3"/>
     </row>
-    <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+    <row r="2" customFormat="false" ht="27.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="4"/>
-      <c r="AF2" s="3"/>
-      <c r="AG2" s="3"/>
-      <c r="AH2" s="5"/>
-      <c r="AI2" s="5"/>
-      <c r="AJ2" s="5"/>
-      <c r="AK2" s="5"/>
-      <c r="AL2" s="5"/>
-      <c r="AM2" s="5"/>
-      <c r="AN2" s="5"/>
-      <c r="AO2" s="5"/>
-      <c r="AP2" s="6"/>
-      <c r="AQ2" s="5"/>
-      <c r="AR2" s="5"/>
-      <c r="AS2" s="5"/>
-      <c r="AT2" s="5"/>
-      <c r="AU2" s="5"/>
-      <c r="AV2" s="5"/>
-      <c r="AW2" s="5"/>
-      <c r="AX2" s="5"/>
-      <c r="AY2" s="5"/>
-      <c r="AZ2" s="5"/>
-      <c r="BA2" s="5"/>
-      <c r="BB2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="4"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="4"/>
+      <c r="AG2" s="4"/>
+      <c r="AH2" s="6"/>
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="6"/>
+      <c r="AK2" s="6"/>
+      <c r="AL2" s="6"/>
+      <c r="AM2" s="6"/>
+      <c r="AN2" s="6"/>
+      <c r="AO2" s="6"/>
+      <c r="AP2" s="7"/>
+      <c r="AQ2" s="6"/>
+      <c r="AR2" s="6"/>
+      <c r="AS2" s="6"/>
+      <c r="AT2" s="6"/>
+      <c r="AU2" s="6"/>
+      <c r="AV2" s="6"/>
+      <c r="AW2" s="6"/>
+      <c r="AX2" s="6"/>
+      <c r="AY2" s="6"/>
+      <c r="AZ2" s="6"/>
+      <c r="BA2" s="6"/>
+      <c r="BB2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4"/>
-      <c r="AA3" s="4"/>
-      <c r="AB3" s="4"/>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="4"/>
-      <c r="AE3" s="4"/>
-      <c r="AF3" s="3"/>
-      <c r="AG3" s="3"/>
-      <c r="AH3" s="4"/>
-      <c r="AI3" s="4"/>
-      <c r="AJ3" s="4"/>
-      <c r="AK3" s="4"/>
-      <c r="AL3" s="4"/>
-      <c r="AM3" s="4"/>
-      <c r="AN3" s="4"/>
-      <c r="AO3" s="4"/>
-      <c r="AP3" s="7" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
+      <c r="AC3" s="4"/>
+      <c r="AD3" s="5"/>
+      <c r="AE3" s="5"/>
+      <c r="AF3" s="4"/>
+      <c r="AG3" s="4"/>
+      <c r="AH3" s="5"/>
+      <c r="AI3" s="5"/>
+      <c r="AJ3" s="5"/>
+      <c r="AK3" s="5"/>
+      <c r="AL3" s="5"/>
+      <c r="AM3" s="5"/>
+      <c r="AN3" s="5"/>
+      <c r="AO3" s="5"/>
+      <c r="AP3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="AQ3" s="4"/>
-      <c r="AR3" s="4"/>
-      <c r="AS3" s="4"/>
-      <c r="AT3" s="4"/>
-      <c r="AU3" s="4"/>
-      <c r="AV3" s="4"/>
-      <c r="AW3" s="4"/>
-      <c r="AX3" s="4"/>
-      <c r="AY3" s="4"/>
-      <c r="AZ3" s="4"/>
-      <c r="BA3" s="4"/>
-      <c r="BB3" s="4"/>
+      <c r="AQ3" s="5"/>
+      <c r="AR3" s="5"/>
+      <c r="AS3" s="5"/>
+      <c r="AT3" s="5"/>
+      <c r="AU3" s="5"/>
+      <c r="AV3" s="5"/>
+      <c r="AW3" s="5"/>
+      <c r="AX3" s="5"/>
+      <c r="AY3" s="5"/>
+      <c r="AZ3" s="5"/>
+      <c r="BA3" s="5"/>
+      <c r="BB3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="4"/>
-      <c r="AE4" s="4"/>
-      <c r="AF4" s="3"/>
-      <c r="AG4" s="3"/>
-      <c r="AH4" s="4"/>
-      <c r="AI4" s="4"/>
-      <c r="AJ4" s="4"/>
-      <c r="AK4" s="4"/>
-      <c r="AL4" s="4"/>
-      <c r="AM4" s="4"/>
-      <c r="AN4" s="4"/>
-      <c r="AO4" s="4"/>
-      <c r="AP4" s="4"/>
-      <c r="AQ4" s="4"/>
-      <c r="AR4" s="4"/>
-      <c r="AS4" s="4"/>
-      <c r="AT4" s="4"/>
-      <c r="AU4" s="4"/>
-      <c r="AV4" s="4"/>
-      <c r="AW4" s="4"/>
-      <c r="AX4" s="4"/>
-      <c r="AY4" s="4"/>
-      <c r="AZ4" s="4"/>
-      <c r="BA4" s="4"/>
-      <c r="BB4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="4"/>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="4"/>
+      <c r="AG4" s="4"/>
+      <c r="AH4" s="5"/>
+      <c r="AI4" s="5"/>
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="5"/>
+      <c r="AL4" s="5"/>
+      <c r="AM4" s="5"/>
+      <c r="AN4" s="5"/>
+      <c r="AO4" s="5"/>
+      <c r="AP4" s="5"/>
+      <c r="AQ4" s="5"/>
+      <c r="AR4" s="5"/>
+      <c r="AS4" s="5"/>
+      <c r="AT4" s="5"/>
+      <c r="AU4" s="5"/>
+      <c r="AV4" s="5"/>
+      <c r="AW4" s="5"/>
+      <c r="AX4" s="5"/>
+      <c r="AY4" s="5"/>
+      <c r="AZ4" s="5"/>
+      <c r="BA4" s="5"/>
+      <c r="BB4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
@@ -2064,15 +2033,15 @@
       <c r="A25" s="20"/>
       <c r="B25" s="20"/>
       <c r="C25" s="21"/>
-      <c r="H25" s="23"/>
+      <c r="H25" s="21"/>
       <c r="I25" s="21"/>
       <c r="J25" s="21"/>
       <c r="K25" s="21"/>
-      <c r="L25" s="23"/>
+      <c r="L25" s="21"/>
       <c r="M25" s="21"/>
       <c r="N25" s="21"/>
       <c r="O25" s="21"/>
-      <c r="P25" s="23"/>
+      <c r="P25" s="21"/>
       <c r="Q25" s="21"/>
       <c r="R25" s="21"/>
       <c r="S25" s="21"/>
@@ -2111,38 +2080,38 @@
       <c r="AZ25" s="21"/>
       <c r="BA25" s="21"/>
       <c r="BB25" s="21"/>
-      <c r="ALS25" s="0"/>
-      <c r="ALT25" s="0"/>
-      <c r="ALU25" s="0"/>
-      <c r="ALV25" s="0"/>
-      <c r="ALW25" s="0"/>
-      <c r="ALX25" s="0"/>
-      <c r="ALY25" s="0"/>
-      <c r="ALZ25" s="0"/>
-      <c r="AMA25" s="0"/>
-      <c r="AMB25" s="0"/>
-      <c r="AMC25" s="0"/>
-      <c r="AMD25" s="0"/>
-      <c r="AME25" s="0"/>
-      <c r="AMF25" s="0"/>
-      <c r="AMG25" s="0"/>
-      <c r="AMH25" s="0"/>
-      <c r="AMI25" s="0"/>
-      <c r="AMJ25" s="0"/>
+      <c r="ALS25" s="2"/>
+      <c r="ALT25" s="2"/>
+      <c r="ALU25" s="2"/>
+      <c r="ALV25" s="2"/>
+      <c r="ALW25" s="2"/>
+      <c r="ALX25" s="2"/>
+      <c r="ALY25" s="2"/>
+      <c r="ALZ25" s="2"/>
+      <c r="AMA25" s="2"/>
+      <c r="AMB25" s="2"/>
+      <c r="AMC25" s="2"/>
+      <c r="AMD25" s="2"/>
+      <c r="AME25" s="2"/>
+      <c r="AMF25" s="2"/>
+      <c r="AMG25" s="2"/>
+      <c r="AMH25" s="2"/>
+      <c r="AMI25" s="2"/>
+      <c r="AMJ25" s="2"/>
     </row>
     <row r="26" s="22" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20"/>
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
-      <c r="H26" s="23"/>
+      <c r="H26" s="21"/>
       <c r="I26" s="21"/>
       <c r="J26" s="21"/>
       <c r="K26" s="21"/>
-      <c r="L26" s="23"/>
+      <c r="L26" s="21"/>
       <c r="M26" s="21"/>
       <c r="N26" s="21"/>
       <c r="O26" s="21"/>
-      <c r="P26" s="23"/>
+      <c r="P26" s="21"/>
       <c r="Q26" s="21"/>
       <c r="S26" s="21"/>
       <c r="T26" s="21"/>
@@ -2178,38 +2147,38 @@
       <c r="AZ26" s="21"/>
       <c r="BA26" s="21"/>
       <c r="BB26" s="21"/>
-      <c r="ALS26" s="0"/>
-      <c r="ALT26" s="0"/>
-      <c r="ALU26" s="0"/>
-      <c r="ALV26" s="0"/>
-      <c r="ALW26" s="0"/>
-      <c r="ALX26" s="0"/>
-      <c r="ALY26" s="0"/>
-      <c r="ALZ26" s="0"/>
-      <c r="AMA26" s="0"/>
-      <c r="AMB26" s="0"/>
-      <c r="AMC26" s="0"/>
-      <c r="AMD26" s="0"/>
-      <c r="AME26" s="0"/>
-      <c r="AMF26" s="0"/>
-      <c r="AMG26" s="0"/>
-      <c r="AMH26" s="0"/>
-      <c r="AMI26" s="0"/>
-      <c r="AMJ26" s="0"/>
+      <c r="ALS26" s="2"/>
+      <c r="ALT26" s="2"/>
+      <c r="ALU26" s="2"/>
+      <c r="ALV26" s="2"/>
+      <c r="ALW26" s="2"/>
+      <c r="ALX26" s="2"/>
+      <c r="ALY26" s="2"/>
+      <c r="ALZ26" s="2"/>
+      <c r="AMA26" s="2"/>
+      <c r="AMB26" s="2"/>
+      <c r="AMC26" s="2"/>
+      <c r="AMD26" s="2"/>
+      <c r="AME26" s="2"/>
+      <c r="AMF26" s="2"/>
+      <c r="AMG26" s="2"/>
+      <c r="AMH26" s="2"/>
+      <c r="AMI26" s="2"/>
+      <c r="AMJ26" s="2"/>
     </row>
     <row r="27" s="22" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21"/>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
-      <c r="H27" s="23"/>
+      <c r="H27" s="21"/>
       <c r="I27" s="21"/>
       <c r="J27" s="21"/>
       <c r="K27" s="21"/>
-      <c r="L27" s="23"/>
+      <c r="L27" s="21"/>
       <c r="M27" s="21"/>
       <c r="N27" s="21"/>
       <c r="O27" s="21"/>
-      <c r="P27" s="23"/>
+      <c r="P27" s="21"/>
       <c r="Q27" s="21"/>
       <c r="S27" s="21"/>
       <c r="T27" s="21"/>
@@ -2245,94 +2214,94 @@
       <c r="AZ27" s="21"/>
       <c r="BA27" s="21"/>
       <c r="BB27" s="21"/>
-      <c r="ALS27" s="0"/>
-      <c r="ALT27" s="0"/>
-      <c r="ALU27" s="0"/>
-      <c r="ALV27" s="0"/>
-      <c r="ALW27" s="0"/>
-      <c r="ALX27" s="0"/>
-      <c r="ALY27" s="0"/>
-      <c r="ALZ27" s="0"/>
-      <c r="AMA27" s="0"/>
-      <c r="AMB27" s="0"/>
-      <c r="AMC27" s="0"/>
-      <c r="AMD27" s="0"/>
-      <c r="AME27" s="0"/>
-      <c r="AMF27" s="0"/>
-      <c r="AMG27" s="0"/>
-      <c r="AMH27" s="0"/>
-      <c r="AMI27" s="0"/>
-      <c r="AMJ27" s="0"/>
+      <c r="ALS27" s="2"/>
+      <c r="ALT27" s="2"/>
+      <c r="ALU27" s="2"/>
+      <c r="ALV27" s="2"/>
+      <c r="ALW27" s="2"/>
+      <c r="ALX27" s="2"/>
+      <c r="ALY27" s="2"/>
+      <c r="ALZ27" s="2"/>
+      <c r="AMA27" s="2"/>
+      <c r="AMB27" s="2"/>
+      <c r="AMC27" s="2"/>
+      <c r="AMD27" s="2"/>
+      <c r="AME27" s="2"/>
+      <c r="AMF27" s="2"/>
+      <c r="AMG27" s="2"/>
+      <c r="AMH27" s="2"/>
+      <c r="AMI27" s="2"/>
+      <c r="AMJ27" s="2"/>
     </row>
-    <row r="28" s="25" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24"/>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="26"/>
-      <c r="M28" s="24"/>
-      <c r="N28" s="24"/>
-      <c r="O28" s="24"/>
-      <c r="P28" s="26"/>
-      <c r="Q28" s="24"/>
-      <c r="R28" s="24"/>
-      <c r="S28" s="24"/>
-      <c r="T28" s="24"/>
-      <c r="U28" s="24"/>
-      <c r="V28" s="24"/>
-      <c r="W28" s="24"/>
-      <c r="X28" s="24"/>
-      <c r="Y28" s="24"/>
-      <c r="Z28" s="24"/>
-      <c r="AA28" s="24"/>
-      <c r="AB28" s="24"/>
-      <c r="AC28" s="24"/>
-      <c r="AD28" s="24"/>
-      <c r="AE28" s="24"/>
-      <c r="AF28" s="24"/>
-      <c r="AG28" s="24"/>
-      <c r="AH28" s="24"/>
-      <c r="AI28" s="24"/>
-      <c r="AJ28" s="24"/>
-      <c r="AK28" s="24"/>
-      <c r="AL28" s="24"/>
-      <c r="AM28" s="24"/>
-      <c r="AN28" s="24"/>
-      <c r="AO28" s="24"/>
-      <c r="AP28" s="24"/>
-      <c r="AQ28" s="24"/>
-      <c r="AR28" s="24"/>
-      <c r="AS28" s="24"/>
-      <c r="AT28" s="24"/>
-      <c r="AU28" s="24"/>
-      <c r="AV28" s="24"/>
-      <c r="AW28" s="24"/>
-      <c r="AX28" s="24"/>
-      <c r="AY28" s="24"/>
-      <c r="AZ28" s="24"/>
-      <c r="BA28" s="24"/>
-      <c r="BB28" s="24"/>
-      <c r="ALS28" s="0"/>
-      <c r="ALT28" s="0"/>
-      <c r="ALU28" s="0"/>
-      <c r="ALV28" s="0"/>
-      <c r="ALW28" s="0"/>
-      <c r="ALX28" s="0"/>
-      <c r="ALY28" s="0"/>
-      <c r="ALZ28" s="0"/>
-      <c r="AMA28" s="0"/>
-      <c r="AMB28" s="0"/>
-      <c r="AMC28" s="0"/>
-      <c r="AMD28" s="0"/>
-      <c r="AME28" s="0"/>
-      <c r="AMF28" s="0"/>
-      <c r="AMG28" s="0"/>
-      <c r="AMH28" s="0"/>
-      <c r="AMI28" s="0"/>
-      <c r="AMJ28" s="0"/>
+    <row r="28" s="24" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="23"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="23"/>
+      <c r="S28" s="23"/>
+      <c r="T28" s="23"/>
+      <c r="U28" s="23"/>
+      <c r="V28" s="23"/>
+      <c r="W28" s="23"/>
+      <c r="X28" s="23"/>
+      <c r="Y28" s="23"/>
+      <c r="Z28" s="23"/>
+      <c r="AA28" s="23"/>
+      <c r="AB28" s="23"/>
+      <c r="AC28" s="23"/>
+      <c r="AD28" s="23"/>
+      <c r="AE28" s="23"/>
+      <c r="AF28" s="23"/>
+      <c r="AG28" s="23"/>
+      <c r="AH28" s="23"/>
+      <c r="AI28" s="23"/>
+      <c r="AJ28" s="23"/>
+      <c r="AK28" s="23"/>
+      <c r="AL28" s="23"/>
+      <c r="AM28" s="23"/>
+      <c r="AN28" s="23"/>
+      <c r="AO28" s="23"/>
+      <c r="AP28" s="23"/>
+      <c r="AQ28" s="23"/>
+      <c r="AR28" s="23"/>
+      <c r="AS28" s="23"/>
+      <c r="AT28" s="23"/>
+      <c r="AU28" s="23"/>
+      <c r="AV28" s="23"/>
+      <c r="AW28" s="23"/>
+      <c r="AX28" s="23"/>
+      <c r="AY28" s="23"/>
+      <c r="AZ28" s="23"/>
+      <c r="BA28" s="23"/>
+      <c r="BB28" s="23"/>
+      <c r="ALS28" s="2"/>
+      <c r="ALT28" s="2"/>
+      <c r="ALU28" s="2"/>
+      <c r="ALV28" s="2"/>
+      <c r="ALW28" s="2"/>
+      <c r="ALX28" s="2"/>
+      <c r="ALY28" s="2"/>
+      <c r="ALZ28" s="2"/>
+      <c r="AMA28" s="2"/>
+      <c r="AMB28" s="2"/>
+      <c r="AMC28" s="2"/>
+      <c r="AMD28" s="2"/>
+      <c r="AME28" s="2"/>
+      <c r="AMF28" s="2"/>
+      <c r="AMG28" s="2"/>
+      <c r="AMH28" s="2"/>
+      <c r="AMI28" s="2"/>
+      <c r="AMJ28" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="86">
@@ -2432,40 +2401,4 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
 </file>